--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y691"/>
+  <dimension ref="A1:Y699"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -81071,6 +81071,942 @@
         <v>46226.0</v>
       </c>
     </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>FS683</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>510492000001426004</t>
+        </is>
+      </c>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D692" s="2" t="inlineStr">
+        <is>
+          <t>510492000000639001</t>
+        </is>
+      </c>
+      <c r="E692" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F692" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G692" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H692" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I692" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J692" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K692" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L692" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M692" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="N692" s="2" t="inlineStr">
+        <is>
+          <t>De'Osa Engineering Services</t>
+        </is>
+      </c>
+      <c r="O692" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P692" s="5" t="n">
+        <v>46232.0</v>
+      </c>
+      <c r="Q692" s="6" t="n">
+        <v>46237.51871527778</v>
+      </c>
+      <c r="R692" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S692" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T692" s="2" t="inlineStr">
+        <is>
+          <t>510492000001426008</t>
+        </is>
+      </c>
+      <c r="U692" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V692" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W692" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X692" s="2" t="inlineStr">
+        <is>
+          <t>242025</t>
+        </is>
+      </c>
+      <c r="Y692" s="5" t="n">
+        <v>46226.0</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="inlineStr">
+        <is>
+          <t>FS684</t>
+        </is>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>510492000001426021</t>
+        </is>
+      </c>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D693" s="2" t="inlineStr">
+        <is>
+          <t>510492000001391001</t>
+        </is>
+      </c>
+      <c r="E693" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F693" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G693" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I693" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J693" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K693" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L693" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M693" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="N693" s="2" t="inlineStr">
+        <is>
+          <t>PAVS DRIVING SCHOOL</t>
+        </is>
+      </c>
+      <c r="O693" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P693" s="5" t="n">
+        <v>46234.0</v>
+      </c>
+      <c r="Q693" s="6" t="n">
+        <v>46237.51925925926</v>
+      </c>
+      <c r="R693" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S693" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T693" s="2" t="inlineStr">
+        <is>
+          <t>510492000001426025</t>
+        </is>
+      </c>
+      <c r="U693" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V693" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W693" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X693" s="2" t="inlineStr">
+        <is>
+          <t>242030</t>
+        </is>
+      </c>
+      <c r="Y693" s="5" t="n">
+        <v>46234.0</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>FS685</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436002</t>
+        </is>
+      </c>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D694" s="2" t="inlineStr">
+        <is>
+          <t>510492000001155001</t>
+        </is>
+      </c>
+      <c r="E694" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F694" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G694" s="2" t="inlineStr">
+        <is>
+          <t>360.000</t>
+        </is>
+      </c>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I694" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J694" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K694" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L694" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M694" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="N694" s="2" t="inlineStr">
+        <is>
+          <t>Galloway Pest Control</t>
+        </is>
+      </c>
+      <c r="O694" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P694" s="5" t="n">
+        <v>46238.0</v>
+      </c>
+      <c r="Q694" s="6" t="n">
+        <v>46241.47833333333</v>
+      </c>
+      <c r="R694" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S694" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T694" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436006</t>
+        </is>
+      </c>
+      <c r="U694" s="2" t="n">
+        <v>360.0</v>
+      </c>
+      <c r="V694" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W694" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X694" s="2" t="inlineStr">
+        <is>
+          <t>242059</t>
+        </is>
+      </c>
+      <c r="Y694" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>FS686</t>
+        </is>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436019</t>
+        </is>
+      </c>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D695" s="2" t="inlineStr">
+        <is>
+          <t>510492000001429142</t>
+        </is>
+      </c>
+      <c r="E695" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F695" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G695" s="2" t="inlineStr">
+        <is>
+          <t>150.000</t>
+        </is>
+      </c>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I695" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J695" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K695" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L695" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M695" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="N695" s="2" t="inlineStr">
+        <is>
+          <t>NIFINSPIRED SKINCARE LTD</t>
+        </is>
+      </c>
+      <c r="O695" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P695" s="5" t="n">
+        <v>46240.0</v>
+      </c>
+      <c r="Q695" s="6" t="n">
+        <v>46241.47866898148</v>
+      </c>
+      <c r="R695" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S695" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T695" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436023</t>
+        </is>
+      </c>
+      <c r="U695" s="2" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="V695" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W695" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X695" s="2" t="inlineStr">
+        <is>
+          <t>242061</t>
+        </is>
+      </c>
+      <c r="Y695" s="5" t="n">
+        <v>46239.0</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>FS687</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436036</t>
+        </is>
+      </c>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D696" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E696" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F696" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G696" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I696" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J696" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K696" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L696" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M696" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="N696" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O696" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P696" s="5" t="n">
+        <v>46241.0</v>
+      </c>
+      <c r="Q696" s="6" t="n">
+        <v>46241.47974537037</v>
+      </c>
+      <c r="R696" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S696" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T696" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436040</t>
+        </is>
+      </c>
+      <c r="U696" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V696" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W696" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X696" s="2" t="inlineStr">
+        <is>
+          <t>241913</t>
+        </is>
+      </c>
+      <c r="Y696" s="5" t="n">
+        <v>46143.0</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="inlineStr">
+        <is>
+          <t>FS688</t>
+        </is>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436053</t>
+        </is>
+      </c>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D697" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E697" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F697" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G697" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I697" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J697" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K697" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L697" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M697" s="2" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="N697" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O697" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P697" s="5" t="n">
+        <v>46241.0</v>
+      </c>
+      <c r="Q697" s="6" t="n">
+        <v>46241.47990740741</v>
+      </c>
+      <c r="R697" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S697" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T697" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436057</t>
+        </is>
+      </c>
+      <c r="U697" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V697" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W697" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X697" s="2" t="inlineStr">
+        <is>
+          <t>241932</t>
+        </is>
+      </c>
+      <c r="Y697" s="5" t="n">
+        <v>46143.0</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>FS689</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436070</t>
+        </is>
+      </c>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D698" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E698" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F698" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G698" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I698" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J698" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K698" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L698" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M698" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="N698" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O698" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P698" s="5" t="n">
+        <v>46241.0</v>
+      </c>
+      <c r="Q698" s="6" t="n">
+        <v>46241.48012731481</v>
+      </c>
+      <c r="R698" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S698" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T698" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436074</t>
+        </is>
+      </c>
+      <c r="U698" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V698" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W698" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X698" s="2" t="inlineStr">
+        <is>
+          <t>241950</t>
+        </is>
+      </c>
+      <c r="Y698" s="5" t="n">
+        <v>46174.0</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>FS690</t>
+        </is>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436087</t>
+        </is>
+      </c>
+      <c r="C699" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D699" s="2" t="inlineStr">
+        <is>
+          <t>510492000000122647</t>
+        </is>
+      </c>
+      <c r="E699" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F699" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G699" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I699" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J699" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K699" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L699" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M699" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="N699" s="2" t="inlineStr">
+        <is>
+          <t>BRIGGS INDUSTRIAL FOOTWEAR LIMITED</t>
+        </is>
+      </c>
+      <c r="O699" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P699" s="5" t="n">
+        <v>46241.0</v>
+      </c>
+      <c r="Q699" s="6" t="n">
+        <v>46241.48064814815</v>
+      </c>
+      <c r="R699" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S699" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T699" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436091</t>
+        </is>
+      </c>
+      <c r="U699" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V699" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W699" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X699" s="2" t="inlineStr">
+        <is>
+          <t>241947</t>
+        </is>
+      </c>
+      <c r="Y699" s="5" t="n">
+        <v>46174.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y699"/>
+  <dimension ref="A1:Y700"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -82007,6 +82007,123 @@
         <v>46174.0</v>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>FS691</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>510492000001445004</t>
+        </is>
+      </c>
+      <c r="C700" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D700" s="2" t="inlineStr">
+        <is>
+          <t>510492000001324001</t>
+        </is>
+      </c>
+      <c r="E700" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F700" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G700" s="2" t="inlineStr">
+        <is>
+          <t>1000.000</t>
+        </is>
+      </c>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I700" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J700" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K700" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L700" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M700" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="N700" s="2" t="inlineStr">
+        <is>
+          <t>READING PROPERTIES GROUP LTD</t>
+        </is>
+      </c>
+      <c r="O700" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P700" s="5" t="n">
+        <v>46237.0</v>
+      </c>
+      <c r="Q700" s="6" t="n">
+        <v>46244.39891203704</v>
+      </c>
+      <c r="R700" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S700" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T700" s="2" t="inlineStr">
+        <is>
+          <t>510492000001445008</t>
+        </is>
+      </c>
+      <c r="U700" s="2" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="V700" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W700" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X700" s="2" t="inlineStr">
+        <is>
+          <t>242064</t>
+        </is>
+      </c>
+      <c r="Y700" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y700"/>
+  <dimension ref="A1:Y705"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -82124,6 +82124,591 @@
         <v>46235.0</v>
       </c>
     </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>FS692</t>
+        </is>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450060</t>
+        </is>
+      </c>
+      <c r="C701" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D701" s="2" t="inlineStr">
+        <is>
+          <t>510492000001025001</t>
+        </is>
+      </c>
+      <c r="E701" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F701" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G701" s="2" t="inlineStr">
+        <is>
+          <t>355.200</t>
+        </is>
+      </c>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I701" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J701" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K701" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L701" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M701" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="N701" s="2" t="inlineStr">
+        <is>
+          <t>Kumon Wokingham &amp; Kumon Ditton &amp; Moseley &amp; Kumon Sandhurst</t>
+        </is>
+      </c>
+      <c r="O701" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P701" s="5" t="n">
+        <v>46244.0</v>
+      </c>
+      <c r="Q701" s="6" t="n">
+        <v>46248.735</v>
+      </c>
+      <c r="R701" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S701" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T701" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450064</t>
+        </is>
+      </c>
+      <c r="U701" s="2" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="V701" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W701" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X701" s="2" t="inlineStr">
+        <is>
+          <t>242029</t>
+        </is>
+      </c>
+      <c r="Y701" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>FS693</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450077</t>
+        </is>
+      </c>
+      <c r="C702" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D702" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436106</t>
+        </is>
+      </c>
+      <c r="E702" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F702" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G702" s="2" t="inlineStr">
+        <is>
+          <t>100.000</t>
+        </is>
+      </c>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I702" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J702" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K702" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L702" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M702" s="2" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="N702" s="2" t="inlineStr">
+        <is>
+          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
+        </is>
+      </c>
+      <c r="O702" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P702" s="5" t="n">
+        <v>46244.0</v>
+      </c>
+      <c r="Q702" s="6" t="n">
+        <v>46248.73539351852</v>
+      </c>
+      <c r="R702" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S702" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T702" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450081</t>
+        </is>
+      </c>
+      <c r="U702" s="2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="V702" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W702" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X702" s="2" t="inlineStr">
+        <is>
+          <t>242062</t>
+        </is>
+      </c>
+      <c r="Y702" s="5" t="n">
+        <v>46241.0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>FS694</t>
+        </is>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450094</t>
+        </is>
+      </c>
+      <c r="C703" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D703" s="2" t="inlineStr">
+        <is>
+          <t>510492000000742001</t>
+        </is>
+      </c>
+      <c r="E703" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F703" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G703" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I703" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J703" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K703" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L703" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M703" s="2" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="N703" s="2" t="inlineStr">
+        <is>
+          <t>Adam’s Painting and Decorating</t>
+        </is>
+      </c>
+      <c r="O703" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P703" s="5" t="n">
+        <v>46244.0</v>
+      </c>
+      <c r="Q703" s="6" t="n">
+        <v>46248.73564814815</v>
+      </c>
+      <c r="R703" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S703" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T703" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450098</t>
+        </is>
+      </c>
+      <c r="U703" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V703" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W703" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X703" s="2" t="inlineStr">
+        <is>
+          <t>242046</t>
+        </is>
+      </c>
+      <c r="Y703" s="5" t="n">
+        <v>46235.0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>FS695</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450111</t>
+        </is>
+      </c>
+      <c r="C704" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D704" s="2" t="inlineStr">
+        <is>
+          <t>510492000000541229</t>
+        </is>
+      </c>
+      <c r="E704" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F704" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G704" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I704" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J704" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K704" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L704" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M704" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="N704" s="2" t="inlineStr">
+        <is>
+          <t>Optimum Global Care</t>
+        </is>
+      </c>
+      <c r="O704" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P704" s="5" t="n">
+        <v>46245.0</v>
+      </c>
+      <c r="Q704" s="6" t="n">
+        <v>46248.73605324074</v>
+      </c>
+      <c r="R704" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S704" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T704" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450115</t>
+        </is>
+      </c>
+      <c r="U704" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V704" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W704" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X704" s="2" t="inlineStr">
+        <is>
+          <t>242066</t>
+        </is>
+      </c>
+      <c r="Y704" s="5" t="n">
+        <v>46245.0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>FS696</t>
+        </is>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450128</t>
+        </is>
+      </c>
+      <c r="C705" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D705" s="2" t="inlineStr">
+        <is>
+          <t>510492000000541229</t>
+        </is>
+      </c>
+      <c r="E705" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F705" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G705" s="2" t="inlineStr">
+        <is>
+          <t>300.000</t>
+        </is>
+      </c>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I705" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J705" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K705" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L705" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M705" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="N705" s="2" t="inlineStr">
+        <is>
+          <t>Optimum Global Care</t>
+        </is>
+      </c>
+      <c r="O705" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P705" s="5" t="n">
+        <v>46248.0</v>
+      </c>
+      <c r="Q705" s="6" t="n">
+        <v>46248.736238425925</v>
+      </c>
+      <c r="R705" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S705" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T705" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450132</t>
+        </is>
+      </c>
+      <c r="U705" s="2" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="V705" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W705" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X705" s="2" t="inlineStr">
+        <is>
+          <t>242069</t>
+        </is>
+      </c>
+      <c r="Y705" s="5" t="n">
+        <v>46248.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y705"/>
+  <dimension ref="A1:Y706"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -82709,6 +82709,123 @@
         <v>46248.0</v>
       </c>
     </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>FS697</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>510492000001460021</t>
+        </is>
+      </c>
+      <c r="C706" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D706" s="2" t="inlineStr">
+        <is>
+          <t>510492000001413024</t>
+        </is>
+      </c>
+      <c r="E706" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F706" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G706" s="2" t="inlineStr">
+        <is>
+          <t>120.000</t>
+        </is>
+      </c>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I706" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J706" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K706" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L706" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M706" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="N706" s="2" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="O706" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P706" s="5" t="n">
+        <v>46234.0</v>
+      </c>
+      <c r="Q706" s="6" t="n">
+        <v>46253.655069444445</v>
+      </c>
+      <c r="R706" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S706" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T706" s="2" t="inlineStr">
+        <is>
+          <t>510492000001460025</t>
+        </is>
+      </c>
+      <c r="U706" s="2" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="V706" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W706" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X706" s="2" t="inlineStr">
+        <is>
+          <t>242031</t>
+        </is>
+      </c>
+      <c r="Y706" s="5" t="n">
+        <v>46234.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y706"/>
+  <dimension ref="A1:Y714"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -82826,6 +82826,942 @@
         <v>46234.0</v>
       </c>
     </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>FS698</t>
+        </is>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467002</t>
+        </is>
+      </c>
+      <c r="C707" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D707" s="2" t="inlineStr">
+        <is>
+          <t>510492000001450146</t>
+        </is>
+      </c>
+      <c r="E707" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F707" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G707" s="2" t="inlineStr">
+        <is>
+          <t>150.000</t>
+        </is>
+      </c>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I707" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J707" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K707" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L707" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M707" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="N707" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Phone Mobile &amp; Vape</t>
+        </is>
+      </c>
+      <c r="O707" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P707" s="5" t="n">
+        <v>46252.0</v>
+      </c>
+      <c r="Q707" s="6" t="n">
+        <v>46258.53056712963</v>
+      </c>
+      <c r="R707" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S707" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T707" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467006</t>
+        </is>
+      </c>
+      <c r="U707" s="2" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="V707" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W707" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X707" s="2" t="inlineStr">
+        <is>
+          <t>242070</t>
+        </is>
+      </c>
+      <c r="Y707" s="5" t="n">
+        <v>46252.0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>FS699</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467019</t>
+        </is>
+      </c>
+      <c r="C708" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D708" s="2" t="inlineStr">
+        <is>
+          <t>510492000001252008</t>
+        </is>
+      </c>
+      <c r="E708" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F708" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G708" s="2" t="inlineStr">
+        <is>
+          <t>300.000</t>
+        </is>
+      </c>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I708" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J708" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K708" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L708" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M708" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="N708" s="2" t="inlineStr">
+        <is>
+          <t>Surge Productions Ltd</t>
+        </is>
+      </c>
+      <c r="O708" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P708" s="5" t="n">
+        <v>46253.0</v>
+      </c>
+      <c r="Q708" s="6" t="n">
+        <v>46258.53089120371</v>
+      </c>
+      <c r="R708" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S708" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T708" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467023</t>
+        </is>
+      </c>
+      <c r="U708" s="2" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="V708" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W708" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X708" s="2" t="inlineStr">
+        <is>
+          <t>242073</t>
+        </is>
+      </c>
+      <c r="Y708" s="5" t="n">
+        <v>46253.0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>FS700</t>
+        </is>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467036</t>
+        </is>
+      </c>
+      <c r="C709" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D709" s="2" t="inlineStr">
+        <is>
+          <t>510492000000822033</t>
+        </is>
+      </c>
+      <c r="E709" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F709" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G709" s="2" t="inlineStr">
+        <is>
+          <t>1080.000</t>
+        </is>
+      </c>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I709" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J709" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K709" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L709" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M709" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="N709" s="2" t="inlineStr">
+        <is>
+          <t>Sofiya Designs Limited</t>
+        </is>
+      </c>
+      <c r="O709" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P709" s="5" t="n">
+        <v>46253.0</v>
+      </c>
+      <c r="Q709" s="6" t="n">
+        <v>46258.53136574074</v>
+      </c>
+      <c r="R709" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S709" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T709" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467040</t>
+        </is>
+      </c>
+      <c r="U709" s="2" t="n">
+        <v>1080.0</v>
+      </c>
+      <c r="V709" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W709" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X709" s="2" t="inlineStr">
+        <is>
+          <t>242074</t>
+        </is>
+      </c>
+      <c r="Y709" s="5" t="n">
+        <v>46253.0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>FS701</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467053</t>
+        </is>
+      </c>
+      <c r="C710" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D710" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123247</t>
+        </is>
+      </c>
+      <c r="E710" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F710" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G710" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I710" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J710" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K710" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L710" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M710" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="N710" s="2" t="inlineStr">
+        <is>
+          <t>NOMADS CLOTHING LIMITED</t>
+        </is>
+      </c>
+      <c r="O710" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P710" s="5" t="n">
+        <v>46255.0</v>
+      </c>
+      <c r="Q710" s="6" t="n">
+        <v>46258.53429398148</v>
+      </c>
+      <c r="R710" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S710" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T710" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467057</t>
+        </is>
+      </c>
+      <c r="U710" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V710" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W710" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X710" s="2" t="inlineStr">
+        <is>
+          <t>241876</t>
+        </is>
+      </c>
+      <c r="Y710" s="5" t="n">
+        <v>46113.0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>FS703</t>
+        </is>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467099</t>
+        </is>
+      </c>
+      <c r="C711" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D711" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123247</t>
+        </is>
+      </c>
+      <c r="E711" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F711" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G711" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I711" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J711" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K711" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L711" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M711" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="N711" s="2" t="inlineStr">
+        <is>
+          <t>NOMADS CLOTHING LIMITED</t>
+        </is>
+      </c>
+      <c r="O711" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P711" s="5" t="n">
+        <v>46255.0</v>
+      </c>
+      <c r="Q711" s="6" t="n">
+        <v>46258.535150462965</v>
+      </c>
+      <c r="R711" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S711" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T711" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467103</t>
+        </is>
+      </c>
+      <c r="U711" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V711" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W711" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X711" s="2" t="inlineStr">
+        <is>
+          <t>241912</t>
+        </is>
+      </c>
+      <c r="Y711" s="5" t="n">
+        <v>46143.0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>FS704</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467116</t>
+        </is>
+      </c>
+      <c r="C712" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D712" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123247</t>
+        </is>
+      </c>
+      <c r="E712" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F712" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G712" s="2" t="inlineStr">
+        <is>
+          <t>22.400</t>
+        </is>
+      </c>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I712" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J712" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K712" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L712" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M712" s="2" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="N712" s="2" t="inlineStr">
+        <is>
+          <t>NOMADS CLOTHING LIMITED</t>
+        </is>
+      </c>
+      <c r="O712" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P712" s="5" t="n">
+        <v>46255.0</v>
+      </c>
+      <c r="Q712" s="6" t="n">
+        <v>46258.53607638889</v>
+      </c>
+      <c r="R712" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S712" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T712" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467120</t>
+        </is>
+      </c>
+      <c r="U712" s="2" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V712" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W712" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X712" s="2" t="inlineStr">
+        <is>
+          <t>241949</t>
+        </is>
+      </c>
+      <c r="Y712" s="5" t="n">
+        <v>46174.0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>FS705</t>
+        </is>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467133</t>
+        </is>
+      </c>
+      <c r="C713" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D713" s="2" t="inlineStr">
+        <is>
+          <t>510492000001158053</t>
+        </is>
+      </c>
+      <c r="E713" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F713" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G713" s="2" t="inlineStr">
+        <is>
+          <t>270.000</t>
+        </is>
+      </c>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I713" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J713" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K713" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L713" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M713" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="N713" s="2" t="inlineStr">
+        <is>
+          <t>PRIME GARDEN DESIGN LTD</t>
+        </is>
+      </c>
+      <c r="O713" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P713" s="5" t="n">
+        <v>46255.0</v>
+      </c>
+      <c r="Q713" s="6" t="n">
+        <v>46258.53712962963</v>
+      </c>
+      <c r="R713" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S713" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T713" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467137</t>
+        </is>
+      </c>
+      <c r="U713" s="2" t="n">
+        <v>270.0</v>
+      </c>
+      <c r="V713" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W713" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X713" s="2" t="inlineStr">
+        <is>
+          <t>242078</t>
+        </is>
+      </c>
+      <c r="Y713" s="5" t="n">
+        <v>46255.0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>FS706</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467150</t>
+        </is>
+      </c>
+      <c r="C714" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D714" s="2" t="inlineStr">
+        <is>
+          <t>510492000001436106</t>
+        </is>
+      </c>
+      <c r="E714" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F714" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G714" s="2" t="inlineStr">
+        <is>
+          <t>100.000</t>
+        </is>
+      </c>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I714" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J714" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K714" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L714" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M714" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="N714" s="2" t="inlineStr">
+        <is>
+          <t>RICHMOND TOTO PROFESSIONAL CLEANING LTD</t>
+        </is>
+      </c>
+      <c r="O714" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P714" s="5" t="n">
+        <v>46255.0</v>
+      </c>
+      <c r="Q714" s="6" t="n">
+        <v>46258.537511574075</v>
+      </c>
+      <c r="R714" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S714" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T714" s="2" t="inlineStr">
+        <is>
+          <t>510492000001467154</t>
+        </is>
+      </c>
+      <c r="U714" s="2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="V714" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W714" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X714" s="2" t="inlineStr">
+        <is>
+          <t>242071</t>
+        </is>
+      </c>
+      <c r="Y714" s="5" t="n">
+        <v>46253.0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Customer_Payment_zoho.xlsx
+++ b/Customer_Payment_zoho.xlsx
@@ -86,7 +86,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y714"/>
+  <dimension ref="A1:Y720"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -216,6 +216,9 @@
     <col min="125" max="125" width="19.53125" customWidth="true"/>
     <col min="126" max="126" width="19.53125" customWidth="true"/>
     <col min="127" max="127" width="19.53125" customWidth="true"/>
+    <col min="128" max="128" width="19.53125" customWidth="true"/>
+    <col min="129" max="129" width="19.53125" customWidth="true"/>
+    <col min="130" max="130" width="19.53125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -83759,6 +83762,708 @@
         </is>
       </c>
       <c r="Y714" s="5" t="n">
+        <v>46253.0</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>FS707</t>
+        </is>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477002</t>
+        </is>
+      </c>
+      <c r="C715" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D715" s="2" t="inlineStr">
+        <is>
+          <t>510492000000256001</t>
+        </is>
+      </c>
+      <c r="E715" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F715" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G715" s="2" t="inlineStr">
+        <is>
+          <t>150.000</t>
+        </is>
+      </c>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I715" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J715" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K715" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L715" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M715" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="N715" s="2" t="inlineStr">
+        <is>
+          <t>OPTIMUM GLOBAL LINKS</t>
+        </is>
+      </c>
+      <c r="O715" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P715" s="5" t="n">
+        <v>46258.0</v>
+      </c>
+      <c r="Q715" s="6" t="n">
+        <v>46261.49940972222</v>
+      </c>
+      <c r="R715" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S715" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T715" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477006</t>
+        </is>
+      </c>
+      <c r="U715" s="2" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="V715" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W715" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X715" s="2" t="inlineStr">
+        <is>
+          <t>242079</t>
+        </is>
+      </c>
+      <c r="Y715" s="5" t="n">
+        <v>46258.0</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>FS708</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477019</t>
+        </is>
+      </c>
+      <c r="C716" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D716" s="2" t="inlineStr">
+        <is>
+          <t>510492000001088061</t>
+        </is>
+      </c>
+      <c r="E716" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F716" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G716" s="2" t="inlineStr">
+        <is>
+          <t>150.000</t>
+        </is>
+      </c>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I716" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J716" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K716" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L716" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M716" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="N716" s="2" t="inlineStr">
+        <is>
+          <t>Drive with Greta</t>
+        </is>
+      </c>
+      <c r="O716" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P716" s="5" t="n">
+        <v>46260.0</v>
+      </c>
+      <c r="Q716" s="6" t="n">
+        <v>46261.49978009259</v>
+      </c>
+      <c r="R716" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S716" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T716" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477023</t>
+        </is>
+      </c>
+      <c r="U716" s="2" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="V716" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W716" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X716" s="2" t="inlineStr">
+        <is>
+          <t>242014</t>
+        </is>
+      </c>
+      <c r="Y716" s="5" t="n">
+        <v>46212.0</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>FS709</t>
+        </is>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477036</t>
+        </is>
+      </c>
+      <c r="C717" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D717" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E717" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F717" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G717" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I717" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J717" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K717" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L717" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M717" s="2" t="inlineStr">
+        <is>
+          <t>709</t>
+        </is>
+      </c>
+      <c r="N717" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O717" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P717" s="5" t="n">
+        <v>46261.0</v>
+      </c>
+      <c r="Q717" s="6" t="n">
+        <v>46261.50041666667</v>
+      </c>
+      <c r="R717" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S717" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T717" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477040</t>
+        </is>
+      </c>
+      <c r="U717" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V717" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W717" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X717" s="2" t="inlineStr">
+        <is>
+          <t>241950</t>
+        </is>
+      </c>
+      <c r="Y717" s="5" t="n">
+        <v>46174.0</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>FS710</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477053</t>
+        </is>
+      </c>
+      <c r="C718" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D718" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E718" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F718" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G718" s="2" t="inlineStr">
+        <is>
+          <t>240.000</t>
+        </is>
+      </c>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I718" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J718" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K718" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L718" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M718" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="N718" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O718" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P718" s="5" t="n">
+        <v>46261.0</v>
+      </c>
+      <c r="Q718" s="6" t="n">
+        <v>46261.50084490741</v>
+      </c>
+      <c r="R718" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S718" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T718" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477057</t>
+        </is>
+      </c>
+      <c r="U718" s="2" t="n">
+        <v>240.0</v>
+      </c>
+      <c r="V718" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W718" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X718" s="2" t="inlineStr">
+        <is>
+          <t>241968</t>
+        </is>
+      </c>
+      <c r="Y718" s="5" t="n">
+        <v>46174.0</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="inlineStr">
+        <is>
+          <t>FS711</t>
+        </is>
+      </c>
+      <c r="B719" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477070</t>
+        </is>
+      </c>
+      <c r="C719" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D719" s="2" t="inlineStr">
+        <is>
+          <t>510492000000123277</t>
+        </is>
+      </c>
+      <c r="E719" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F719" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G719" s="2" t="inlineStr">
+        <is>
+          <t>238.800</t>
+        </is>
+      </c>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I719" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J719" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K719" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L719" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M719" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="N719" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Shoes Limited</t>
+        </is>
+      </c>
+      <c r="O719" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P719" s="5" t="n">
+        <v>46261.0</v>
+      </c>
+      <c r="Q719" s="6" t="n">
+        <v>46261.501180555555</v>
+      </c>
+      <c r="R719" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S719" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T719" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477074</t>
+        </is>
+      </c>
+      <c r="U719" s="2" t="n">
+        <v>238.8</v>
+      </c>
+      <c r="V719" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W719" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X719" s="2" t="inlineStr">
+        <is>
+          <t>241987</t>
+        </is>
+      </c>
+      <c r="Y719" s="5" t="n">
+        <v>46204.0</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>FS712</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477087</t>
+        </is>
+      </c>
+      <c r="C720" s="2" t="inlineStr">
+        <is>
+          <t>BACS</t>
+        </is>
+      </c>
+      <c r="D720" s="2" t="inlineStr">
+        <is>
+          <t>510492000001413024</t>
+        </is>
+      </c>
+      <c r="E720" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F720" s="2" t="inlineStr">
+        <is>
+          <t>1.000000000000</t>
+        </is>
+      </c>
+      <c r="G720" s="2" t="inlineStr">
+        <is>
+          <t>100.000</t>
+        </is>
+      </c>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I720" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="J720" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K720" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="L720" s="2" t="inlineStr">
+        <is>
+          <t>FS</t>
+        </is>
+      </c>
+      <c r="M720" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="N720" s="2" t="inlineStr">
+        <is>
+          <t>88 DRIVING SCHOOL LTD</t>
+        </is>
+      </c>
+      <c r="O720" s="2" t="inlineStr">
+        <is>
+          <t>Invoice Payment</t>
+        </is>
+      </c>
+      <c r="P720" s="5" t="n">
+        <v>46259.0</v>
+      </c>
+      <c r="Q720" s="6" t="n">
+        <v>46261.502280092594</v>
+      </c>
+      <c r="R720" s="2" t="inlineStr">
+        <is>
+          <t>Petty Cash</t>
+        </is>
+      </c>
+      <c r="S720" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T720" s="2" t="inlineStr">
+        <is>
+          <t>510492000001477091</t>
+        </is>
+      </c>
+      <c r="U720" s="2" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="V720" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W720" s="2" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="X720" s="2" t="inlineStr">
+        <is>
+          <t>242072</t>
+        </is>
+      </c>
+      <c r="Y720" s="5" t="n">
         <v>46253.0</v>
       </c>
     </row>
